--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/73.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/73.xlsx
@@ -426,13 +426,13 @@
         <v>-2.933625599755152</v>
       </c>
       <c r="E2">
-        <v>-8.558944732958205</v>
+        <v>-15.21619361690707</v>
       </c>
       <c r="F2">
-        <v>-2.019564017109716</v>
+        <v>-2.960625006488275</v>
       </c>
       <c r="G2">
-        <v>-11.47640451625198</v>
+        <v>-14.50850500915881</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.930670486433915</v>
       </c>
       <c r="E3">
-        <v>-10.12468463636194</v>
+        <v>-16.17549821550464</v>
       </c>
       <c r="F3">
-        <v>-1.75034543956728</v>
+        <v>-2.846559643490186</v>
       </c>
       <c r="G3">
-        <v>-11.07761719607631</v>
+        <v>-13.56629772920439</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.931473566042503</v>
       </c>
       <c r="E4">
-        <v>-10.69946831766159</v>
+        <v>-15.89933458167149</v>
       </c>
       <c r="F4">
-        <v>-1.894774609714985</v>
+        <v>-3.065974287674108</v>
       </c>
       <c r="G4">
-        <v>-10.64030572871418</v>
+        <v>-13.4266894675669</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.910461417112594</v>
       </c>
       <c r="E5">
-        <v>-9.523474071402411</v>
+        <v>-16.4350199315592</v>
       </c>
       <c r="F5">
-        <v>-1.343560715809332</v>
+        <v>-2.772775302188029</v>
       </c>
       <c r="G5">
-        <v>-11.00758788853658</v>
+        <v>-13.11147208175277</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.844754480658068</v>
       </c>
       <c r="E6">
-        <v>-11.82272508651809</v>
+        <v>-16.71698144840181</v>
       </c>
       <c r="F6">
-        <v>-1.072901607353427</v>
+        <v>-2.587184555795216</v>
       </c>
       <c r="G6">
-        <v>-10.36154869648724</v>
+        <v>-12.57080123602846</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.711973157387543</v>
       </c>
       <c r="E7">
-        <v>-12.36723601047106</v>
+        <v>-17.84770153800903</v>
       </c>
       <c r="F7">
-        <v>-1.489813122610599</v>
+        <v>-2.914642331958875</v>
       </c>
       <c r="G7">
-        <v>-10.0186874415701</v>
+        <v>-12.35878005703956</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.488776934389992</v>
       </c>
       <c r="E8">
-        <v>-13.03375997672484</v>
+        <v>-18.29806746765079</v>
       </c>
       <c r="F8">
-        <v>-1.382233048009027</v>
+        <v>-2.803764526726758</v>
       </c>
       <c r="G8">
-        <v>-9.53156166203723</v>
+        <v>-12.18271666330406</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.158796881754593</v>
       </c>
       <c r="E9">
-        <v>-12.51381945096956</v>
+        <v>-18.7083466015853</v>
       </c>
       <c r="F9">
-        <v>-1.427630066784648</v>
+        <v>-2.693992591977379</v>
       </c>
       <c r="G9">
-        <v>-9.422569602219728</v>
+        <v>-11.2187527432996</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.71570087332386</v>
       </c>
       <c r="E10">
-        <v>-14.31753836328597</v>
+        <v>-19.39744742460086</v>
       </c>
       <c r="F10">
-        <v>-1.46990248371691</v>
+        <v>-2.594939731420225</v>
       </c>
       <c r="G10">
-        <v>-8.858386390707851</v>
+        <v>-10.79417257193603</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.170582429030619</v>
       </c>
       <c r="E11">
-        <v>-15.27624489945277</v>
+        <v>-19.77552255792265</v>
       </c>
       <c r="F11">
-        <v>-1.181202361595435</v>
+        <v>-2.430343956851366</v>
       </c>
       <c r="G11">
-        <v>-8.282950870008277</v>
+        <v>-10.33313465772986</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5530201169061262</v>
       </c>
       <c r="E12">
-        <v>-15.32521541418382</v>
+        <v>-20.35411058079584</v>
       </c>
       <c r="F12">
-        <v>-0.7551829467444826</v>
+        <v>-2.453027969809628</v>
       </c>
       <c r="G12">
-        <v>-7.664859698806797</v>
+        <v>-9.842238963007416</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.09747252270421879</v>
       </c>
       <c r="E13">
-        <v>-16.52003201416712</v>
+        <v>-21.14110674794892</v>
       </c>
       <c r="F13">
-        <v>-1.218311564506047</v>
+        <v>-2.226727935773636</v>
       </c>
       <c r="G13">
-        <v>-7.347649009497351</v>
+        <v>-9.352643419091351</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.7331721426301314</v>
       </c>
       <c r="E14">
-        <v>-17.66819143812729</v>
+        <v>-22.08683865193695</v>
       </c>
       <c r="F14">
-        <v>-0.818668196127634</v>
+        <v>-2.116003378511038</v>
       </c>
       <c r="G14">
-        <v>-6.521275245561445</v>
+        <v>-8.521431945428111</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.315053154176688</v>
       </c>
       <c r="E15">
-        <v>-17.10180555012645</v>
+        <v>-22.99183585925107</v>
       </c>
       <c r="F15">
-        <v>-0.299529516425781</v>
+        <v>-2.131850875293995</v>
       </c>
       <c r="G15">
-        <v>-6.595848554062004</v>
+        <v>-7.713179359699122</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.81117171668364</v>
       </c>
       <c r="E16">
-        <v>-18.89312297342693</v>
+        <v>-23.56609623592378</v>
       </c>
       <c r="F16">
-        <v>-0.1332215064353355</v>
+        <v>-1.635255386091928</v>
       </c>
       <c r="G16">
-        <v>-5.362078539661235</v>
+        <v>-8.08651061473914</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.209399392873239</v>
       </c>
       <c r="E17">
-        <v>-19.96723479267673</v>
+        <v>-24.3413886535635</v>
       </c>
       <c r="F17">
-        <v>-0.09065004887066325</v>
+        <v>-1.605953545952701</v>
       </c>
       <c r="G17">
-        <v>-6.193924424260114</v>
+        <v>-7.139416020910155</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.509457333066349</v>
       </c>
       <c r="E18">
-        <v>-20.58470517997297</v>
+        <v>-24.62024772154647</v>
       </c>
       <c r="F18">
-        <v>0.009440756042198213</v>
+        <v>-1.263315108765338</v>
       </c>
       <c r="G18">
-        <v>-5.191126983835137</v>
+        <v>-7.590889472306785</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.725254232997855</v>
       </c>
       <c r="E19">
-        <v>-21.19465410155994</v>
+        <v>-25.69321740768195</v>
       </c>
       <c r="F19">
-        <v>0.8183415248759155</v>
+        <v>-0.9346512296632039</v>
       </c>
       <c r="G19">
-        <v>-3.761321379576853</v>
+        <v>-7.150334154790191</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.877084324020619</v>
       </c>
       <c r="E20">
-        <v>-23.31241393499193</v>
+        <v>-26.64463090476234</v>
       </c>
       <c r="F20">
-        <v>0.5942540601728016</v>
+        <v>-0.5872637621555921</v>
       </c>
       <c r="G20">
-        <v>-4.355477244367005</v>
+        <v>-7.679325834586156</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.986588081671919</v>
       </c>
       <c r="E21">
-        <v>-22.55285388185067</v>
+        <v>-28.05662723134358</v>
       </c>
       <c r="F21">
-        <v>1.040155121058345</v>
+        <v>-0.2210425333779306</v>
       </c>
       <c r="G21">
-        <v>-4.249005858452223</v>
+        <v>-6.974584050405627</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.077051161129879</v>
       </c>
       <c r="E22">
-        <v>-23.93605184110554</v>
+        <v>-27.62488845449368</v>
       </c>
       <c r="F22">
-        <v>1.110057732710984</v>
+        <v>-0.1655046408572378</v>
       </c>
       <c r="G22">
-        <v>-3.928889410412868</v>
+        <v>-7.400607963528084</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.165480881954798</v>
       </c>
       <c r="E23">
-        <v>-23.5790625616799</v>
+        <v>-28.34124472682841</v>
       </c>
       <c r="F23">
-        <v>0.5226856016731327</v>
+        <v>0.1530780069528269</v>
       </c>
       <c r="G23">
-        <v>-3.43621579862388</v>
+        <v>-6.955653541375464</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.270577353245914</v>
       </c>
       <c r="E24">
-        <v>-23.26773368755943</v>
+        <v>-28.03519250769614</v>
       </c>
       <c r="F24">
-        <v>1.623398668960643</v>
+        <v>0.01225057827249414</v>
       </c>
       <c r="G24">
-        <v>-3.342330812382855</v>
+        <v>-6.733359082420533</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.399440835514835</v>
       </c>
       <c r="E25">
-        <v>-24.78885979491185</v>
+        <v>-28.73380626125121</v>
       </c>
       <c r="F25">
-        <v>1.536824334959261</v>
+        <v>0.04879483461439713</v>
       </c>
       <c r="G25">
-        <v>-3.812374490056073</v>
+        <v>-7.650028058784683</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.563072283422347</v>
       </c>
       <c r="E26">
-        <v>-23.61212212382554</v>
+        <v>-28.44790127025567</v>
       </c>
       <c r="F26">
-        <v>1.462993605082547</v>
+        <v>0.6416499294913781</v>
       </c>
       <c r="G26">
-        <v>-3.699679089036077</v>
+        <v>-7.220393485892716</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.760713874190652</v>
       </c>
       <c r="E27">
-        <v>-24.2046898560181</v>
+        <v>-29.18467680606893</v>
       </c>
       <c r="F27">
-        <v>1.53706953171049</v>
+        <v>0.5935391791041856</v>
       </c>
       <c r="G27">
-        <v>-4.286464821845517</v>
+        <v>-7.60377610760852</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.995202617185391</v>
       </c>
       <c r="E28">
-        <v>-23.63598232288668</v>
+        <v>-29.07251518103061</v>
       </c>
       <c r="F28">
-        <v>1.708271536316675</v>
+        <v>0.2165541442945474</v>
       </c>
       <c r="G28">
-        <v>-3.761587675525147</v>
+        <v>-6.987201779014478</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.261221750964458</v>
       </c>
       <c r="E29">
-        <v>-22.99539516135644</v>
+        <v>-28.61835321623796</v>
       </c>
       <c r="F29">
-        <v>1.409300486767888</v>
+        <v>0.1875496880529255</v>
       </c>
       <c r="G29">
-        <v>-4.415459101347833</v>
+        <v>-7.360961196167437</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.552397768955882</v>
       </c>
       <c r="E30">
-        <v>-24.26515230648495</v>
+        <v>-28.70746659502915</v>
       </c>
       <c r="F30">
-        <v>1.443415969884783</v>
+        <v>0.3094977952560548</v>
       </c>
       <c r="G30">
-        <v>-4.571466755134399</v>
+        <v>-7.648216202038451</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.860794128164865</v>
       </c>
       <c r="E31">
-        <v>-23.98140906198399</v>
+        <v>-28.57341339309765</v>
       </c>
       <c r="F31">
-        <v>1.357000682424739</v>
+        <v>0.4736595053058468</v>
       </c>
       <c r="G31">
-        <v>-3.589962547594541</v>
+        <v>-6.692579251907343</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.169333075196469</v>
       </c>
       <c r="E32">
-        <v>-24.05771601365506</v>
+        <v>-27.09806605757315</v>
       </c>
       <c r="F32">
-        <v>1.22568456826335</v>
+        <v>0.1448208406817214</v>
       </c>
       <c r="G32">
-        <v>-4.723699272242214</v>
+        <v>-7.432555645089537</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.470460489393116</v>
       </c>
       <c r="E33">
-        <v>-22.70449593374281</v>
+        <v>-27.55745691542376</v>
       </c>
       <c r="F33">
-        <v>1.56810348808897</v>
+        <v>0.1306143397237099</v>
       </c>
       <c r="G33">
-        <v>-4.477704473889156</v>
+        <v>-7.31783952775602</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.747867969811249</v>
       </c>
       <c r="E34">
-        <v>-21.78014060844367</v>
+        <v>-27.46552973596</v>
       </c>
       <c r="F34">
-        <v>1.320446485674002</v>
+        <v>0.12841585263668</v>
       </c>
       <c r="G34">
-        <v>-4.101817299894439</v>
+        <v>-6.966347151220664</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.998565626763833</v>
       </c>
       <c r="E35">
-        <v>-21.39686980775451</v>
+        <v>-26.60046150232279</v>
       </c>
       <c r="F35">
-        <v>1.611591120001139</v>
+        <v>0.2869761423087418</v>
       </c>
       <c r="G35">
-        <v>-3.691392585703883</v>
+        <v>-7.1151073780223</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.214579433803024</v>
       </c>
       <c r="E36">
-        <v>-21.27589091507358</v>
+        <v>-25.71179056872658</v>
       </c>
       <c r="F36">
-        <v>1.082673563109238</v>
+        <v>0.1051420420876251</v>
       </c>
       <c r="G36">
-        <v>-4.009125423931552</v>
+        <v>-7.335065220568185</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.396346681103925</v>
       </c>
       <c r="E37">
-        <v>-20.20414642627893</v>
+        <v>-25.5315370440177</v>
       </c>
       <c r="F37">
-        <v>1.417116961580704</v>
+        <v>-0.05510066177952247</v>
       </c>
       <c r="G37">
-        <v>-3.532424347550995</v>
+        <v>-6.875200836055718</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.542649493731467</v>
       </c>
       <c r="E38">
-        <v>-20.21189216539973</v>
+        <v>-24.93333755726866</v>
       </c>
       <c r="F38">
-        <v>1.132486608509183</v>
+        <v>-0.2259199606456141</v>
       </c>
       <c r="G38">
-        <v>-4.850309941932844</v>
+        <v>-6.673512984158443</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.65069792885258</v>
       </c>
       <c r="E39">
-        <v>-18.42001405857041</v>
+        <v>-24.20260909714436</v>
       </c>
       <c r="F39">
-        <v>1.560058383872982</v>
+        <v>0.03591372150086481</v>
       </c>
       <c r="G39">
-        <v>-4.821552590261732</v>
+        <v>-6.775172767791803</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.725276559525601</v>
       </c>
       <c r="E40">
-        <v>-18.57578855573075</v>
+        <v>-23.75275401249555</v>
       </c>
       <c r="F40">
-        <v>1.219831324195169</v>
+        <v>0.1261403273811898</v>
       </c>
       <c r="G40">
-        <v>-4.317125406323552</v>
+        <v>-6.787176971421742</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.765379231936184</v>
       </c>
       <c r="E41">
-        <v>-18.04003260125052</v>
+        <v>-23.53922495865215</v>
       </c>
       <c r="F41">
-        <v>1.403109268799365</v>
+        <v>0.1150609133687464</v>
       </c>
       <c r="G41">
-        <v>-4.682937716941162</v>
+        <v>-6.913523955908669</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.779993908354853</v>
       </c>
       <c r="E42">
-        <v>-19.30751378657302</v>
+        <v>-23.17177789311059</v>
       </c>
       <c r="F42">
-        <v>1.001052866176597</v>
+        <v>0.04659469079256164</v>
       </c>
       <c r="G42">
-        <v>-3.955897563207935</v>
+        <v>-6.764113653703848</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.764781382479862</v>
       </c>
       <c r="E43">
-        <v>-17.6431849527405</v>
+        <v>-21.35432846415429</v>
       </c>
       <c r="F43">
-        <v>1.097496369414932</v>
+        <v>-0.1781148778300546</v>
       </c>
       <c r="G43">
-        <v>-4.42056310702346</v>
+        <v>-6.982578150343616</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.721509589559349</v>
       </c>
       <c r="E44">
-        <v>-15.76505710632846</v>
+        <v>-21.08455662255006</v>
       </c>
       <c r="F44">
-        <v>0.6989621849888675</v>
+        <v>-0.03697598300626929</v>
       </c>
       <c r="G44">
-        <v>-4.435107565140552</v>
+        <v>-6.864016406227388</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.641874098946852</v>
       </c>
       <c r="E45">
-        <v>-15.33819835278524</v>
+        <v>-21.27203673496414</v>
       </c>
       <c r="F45">
-        <v>1.029359837065061</v>
+        <v>-0.1250314379238567</v>
       </c>
       <c r="G45">
-        <v>-4.852333268990957</v>
+        <v>-6.663205764512727</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.520960154755921</v>
       </c>
       <c r="E46">
-        <v>-14.70678148186023</v>
+        <v>-20.70094110532094</v>
       </c>
       <c r="F46">
-        <v>0.9423845732407247</v>
+        <v>-0.08968417247899903</v>
       </c>
       <c r="G46">
-        <v>-4.009626686893046</v>
+        <v>-6.946385398077012</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.352071894261196</v>
       </c>
       <c r="E47">
-        <v>-14.3901572633006</v>
+        <v>-19.20004113712043</v>
       </c>
       <c r="F47">
-        <v>0.4656748719102623</v>
+        <v>-0.07636319627458017</v>
       </c>
       <c r="G47">
-        <v>-4.090700749425478</v>
+        <v>-7.489660461530958</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.127746999972016</v>
       </c>
       <c r="E48">
-        <v>-14.42284718963832</v>
+        <v>-20.04738346482327</v>
       </c>
       <c r="F48">
-        <v>1.033244880184191</v>
+        <v>-0.2240263127628145</v>
       </c>
       <c r="G48">
-        <v>-4.778203787070886</v>
+        <v>-7.430182478256215</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.847703986201078</v>
       </c>
       <c r="E49">
-        <v>-13.51677014737975</v>
+        <v>-18.67593494040634</v>
       </c>
       <c r="F49">
-        <v>1.031341291892558</v>
+        <v>-0.08835298606270023</v>
       </c>
       <c r="G49">
-        <v>-5.137282987388017</v>
+        <v>-7.534734966896529</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.507193229568589</v>
       </c>
       <c r="E50">
-        <v>-12.82053410730815</v>
+        <v>-18.14570691019946</v>
       </c>
       <c r="F50">
-        <v>0.6352971798793087</v>
+        <v>-0.2853097615893247</v>
       </c>
       <c r="G50">
-        <v>-4.990360724778525</v>
+        <v>-7.39335009356479</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.110598230859403</v>
       </c>
       <c r="E51">
-        <v>-12.08924911686631</v>
+        <v>-17.86333837864701</v>
       </c>
       <c r="F51">
-        <v>0.7611924577567776</v>
+        <v>-0.493182762750041</v>
       </c>
       <c r="G51">
-        <v>-4.362930920174634</v>
+        <v>-7.767173473960232</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.654382387858703</v>
       </c>
       <c r="E52">
-        <v>-12.2505681511453</v>
+        <v>-16.98419075861863</v>
       </c>
       <c r="F52">
-        <v>0.5934513721594888</v>
+        <v>-0.3252080775451628</v>
       </c>
       <c r="G52">
-        <v>-5.072466031424447</v>
+        <v>-7.492101507723649</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.145642051889194</v>
       </c>
       <c r="E53">
-        <v>-11.38452806605808</v>
+        <v>-17.06228774437071</v>
       </c>
       <c r="F53">
-        <v>0.7690851423706513</v>
+        <v>-0.6397077024268287</v>
       </c>
       <c r="G53">
-        <v>-5.180613515366724</v>
+        <v>-7.974447013910194</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.583993936465942</v>
       </c>
       <c r="E54">
-        <v>-11.14073456129065</v>
+        <v>-16.76509640159995</v>
       </c>
       <c r="F54">
-        <v>0.8916802045153669</v>
+        <v>-0.285671758144348</v>
       </c>
       <c r="G54">
-        <v>-4.988021497624888</v>
+        <v>-8.29008603497579</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.975434153566698</v>
       </c>
       <c r="E55">
-        <v>-10.73927269499874</v>
+        <v>-16.14525868384857</v>
       </c>
       <c r="F55">
-        <v>0.4929513537496444</v>
+        <v>-0.2894905318712538</v>
       </c>
       <c r="G55">
-        <v>-5.853540765959947</v>
+        <v>-7.986503432431954</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.321989598001584</v>
       </c>
       <c r="E56">
-        <v>-10.31502215816751</v>
+        <v>-15.36306778219831</v>
       </c>
       <c r="F56">
-        <v>0.4335880605628235</v>
+        <v>-0.52627272702227</v>
       </c>
       <c r="G56">
-        <v>-5.439095505099077</v>
+        <v>-8.806245905106433</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.629111184011175</v>
       </c>
       <c r="E57">
-        <v>-9.719032179843287</v>
+        <v>-15.5812941180501</v>
       </c>
       <c r="F57">
-        <v>0.6558970204521268</v>
+        <v>-0.3696450185009396</v>
       </c>
       <c r="G57">
-        <v>-6.496846508422398</v>
+        <v>-8.595424363257148</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.9045728636053594</v>
       </c>
       <c r="E58">
-        <v>-9.169894578474459</v>
+        <v>-14.65080865283551</v>
       </c>
       <c r="F58">
-        <v>0.3996904380728649</v>
+        <v>-0.3674316208006593</v>
       </c>
       <c r="G58">
-        <v>-6.611374652145355</v>
+        <v>-9.346839733865306</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.1539897630754323</v>
       </c>
       <c r="E59">
-        <v>-8.738267938330328</v>
+        <v>-14.72215251697342</v>
       </c>
       <c r="F59">
-        <v>0.1403890750767441</v>
+        <v>-0.270917706333086</v>
       </c>
       <c r="G59">
-        <v>-6.544636188162727</v>
+        <v>-8.741483774779276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.6096099276299929</v>
       </c>
       <c r="E60">
-        <v>-9.360124116785579</v>
+        <v>-14.79661959602759</v>
       </c>
       <c r="F60">
-        <v>0.5046926333169246</v>
+        <v>-0.6111919829528586</v>
       </c>
       <c r="G60">
-        <v>-6.980904663060712</v>
+        <v>-9.434418466546497</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.378990906536055</v>
       </c>
       <c r="E61">
-        <v>-8.616421024482507</v>
+        <v>-13.42414938162475</v>
       </c>
       <c r="F61">
-        <v>0.2757774433902953</v>
+        <v>-0.5969805117904302</v>
       </c>
       <c r="G61">
-        <v>-7.336707378915995</v>
+        <v>-9.703921714570233</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.137294772269039</v>
       </c>
       <c r="E62">
-        <v>-8.72514379054387</v>
+        <v>-13.62500698771611</v>
       </c>
       <c r="F62">
-        <v>0.5877165846299078</v>
+        <v>-0.7342476173735307</v>
       </c>
       <c r="G62">
-        <v>-6.744838526387658</v>
+        <v>-9.978061644987788</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.8732604945179</v>
       </c>
       <c r="E63">
-        <v>-7.969412998244093</v>
+        <v>-13.1534389142611</v>
       </c>
       <c r="F63">
-        <v>0.8127682689898804</v>
+        <v>-0.2432643173254302</v>
       </c>
       <c r="G63">
-        <v>-6.8861346344033</v>
+        <v>-10.0701595765562</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.566727192799202</v>
       </c>
       <c r="E64">
-        <v>-8.140105830483222</v>
+        <v>-13.05470046822463</v>
       </c>
       <c r="F64">
-        <v>0.1376380669320469</v>
+        <v>-0.7904763683081584</v>
       </c>
       <c r="G64">
-        <v>-7.682944326589439</v>
+        <v>-9.534654089005404</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.20193869136475</v>
       </c>
       <c r="E65">
-        <v>-6.916171065901549</v>
+        <v>-12.43200949429309</v>
       </c>
       <c r="F65">
-        <v>0.5155831795615298</v>
+        <v>-0.5616075669560858</v>
       </c>
       <c r="G65">
-        <v>-7.089211402423047</v>
+        <v>-9.880948473059853</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.761006765774823</v>
       </c>
       <c r="E66">
-        <v>-6.870572958766257</v>
+        <v>-13.02611391467584</v>
       </c>
       <c r="F66">
-        <v>0.3840342941599543</v>
+        <v>-0.8549059565305012</v>
       </c>
       <c r="G66">
-        <v>-7.470139924223204</v>
+        <v>-9.726494212304999</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.229763432660164</v>
       </c>
       <c r="E67">
-        <v>-7.593231729286423</v>
+        <v>-12.39183548114802</v>
       </c>
       <c r="F67">
-        <v>0.1738692003956917</v>
+        <v>-1.030830483700046</v>
       </c>
       <c r="G67">
-        <v>-7.600875570367793</v>
+        <v>-10.06231951054908</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.600319912483865</v>
       </c>
       <c r="E68">
-        <v>-7.844305813506283</v>
+        <v>-12.60798105812607</v>
       </c>
       <c r="F68">
-        <v>0.03771127876493974</v>
+        <v>-1.010617490704335</v>
       </c>
       <c r="G68">
-        <v>-6.783837829089708</v>
+        <v>-10.35223747590303</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.867570295411998</v>
       </c>
       <c r="E69">
-        <v>-5.615688463391963</v>
+        <v>-12.81783867315833</v>
       </c>
       <c r="F69">
-        <v>-0.146601296725353</v>
+        <v>-0.866371389752649</v>
       </c>
       <c r="G69">
-        <v>-7.935569110831629</v>
+        <v>-10.21541487874426</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.035935265553364</v>
       </c>
       <c r="E70">
-        <v>-6.449171524903853</v>
+        <v>-13.22027654411157</v>
       </c>
       <c r="F70">
-        <v>-0.3607624348407205</v>
+        <v>-0.8483204356782451</v>
       </c>
       <c r="G70">
-        <v>-7.168497104910566</v>
+        <v>-10.31274474247326</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.109616036361162</v>
       </c>
       <c r="E71">
-        <v>-7.422518130990671</v>
+        <v>-12.75800751081285</v>
       </c>
       <c r="F71">
-        <v>-0.1585331007952771</v>
+        <v>-0.9066457845093583</v>
       </c>
       <c r="G71">
-        <v>-6.867146688992133</v>
+        <v>-10.04061769613545</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.10248056957371</v>
       </c>
       <c r="E72">
-        <v>-8.359349703109595</v>
+        <v>-12.31605183410387</v>
       </c>
       <c r="F72">
-        <v>-0.5514666932110143</v>
+        <v>-1.225013885162098</v>
       </c>
       <c r="G72">
-        <v>-7.484551234366149</v>
+        <v>-10.34791147211556</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.023911964598846</v>
       </c>
       <c r="E73">
-        <v>-8.448095522698532</v>
+        <v>-12.63528011616417</v>
       </c>
       <c r="F73">
-        <v>-0.05887304693187142</v>
+        <v>-1.143999553168306</v>
       </c>
       <c r="G73">
-        <v>-6.643076923715244</v>
+        <v>-10.02300430775151</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.887743079862603</v>
       </c>
       <c r="E74">
-        <v>-8.22745201785569</v>
+        <v>-12.90179584008974</v>
       </c>
       <c r="F74">
-        <v>-0.6434949981924281</v>
+        <v>-1.345600984722428</v>
       </c>
       <c r="G74">
-        <v>-7.248059546324743</v>
+        <v>-10.39449759859938</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.699173150602032</v>
       </c>
       <c r="E75">
-        <v>-8.79885913834825</v>
+        <v>-12.83411095512901</v>
       </c>
       <c r="F75">
-        <v>-0.5278880434577291</v>
+        <v>-1.273301906173489</v>
       </c>
       <c r="G75">
-        <v>-5.980762349884897</v>
+        <v>-10.45707453570378</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.466058631000188</v>
       </c>
       <c r="E76">
-        <v>-11.15708990748782</v>
+        <v>-13.80154338828927</v>
       </c>
       <c r="F76">
-        <v>-0.4144770907078516</v>
+        <v>-1.282372529234144</v>
       </c>
       <c r="G76">
-        <v>-6.552742550118134</v>
+        <v>-10.26119950663862</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.188986415077088</v>
       </c>
       <c r="E77">
-        <v>-7.478520032494658</v>
+        <v>-13.81980090527322</v>
       </c>
       <c r="F77">
-        <v>-0.3440791153483384</v>
+        <v>-1.137366815374091</v>
       </c>
       <c r="G77">
-        <v>-6.622804491965249</v>
+        <v>-9.90416060321944</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.867232457440723</v>
       </c>
       <c r="E78">
-        <v>-10.49349395521804</v>
+        <v>-14.39699760235259</v>
       </c>
       <c r="F78">
-        <v>-0.5193467471674634</v>
+        <v>-1.407008688659358</v>
       </c>
       <c r="G78">
-        <v>-6.003598532823365</v>
+        <v>-9.545363363318151</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.496815092943566</v>
       </c>
       <c r="E79">
-        <v>-8.91441809025028</v>
+        <v>-14.7442808269121</v>
       </c>
       <c r="F79">
-        <v>-0.7123977703898882</v>
+        <v>-1.336152626126096</v>
       </c>
       <c r="G79">
-        <v>-5.391757484173011</v>
+        <v>-9.291238706308366</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.072292717982791</v>
       </c>
       <c r="E80">
-        <v>-11.76173933142431</v>
+        <v>-15.44482790033888</v>
       </c>
       <c r="F80">
-        <v>-0.4256890435047429</v>
+        <v>-0.97080283985618</v>
       </c>
       <c r="G80">
-        <v>-5.073170932464047</v>
+        <v>-9.150560039388521</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.592364125152571</v>
       </c>
       <c r="E81">
-        <v>-11.91955305534514</v>
+        <v>-16.62017009242006</v>
       </c>
       <c r="F81">
-        <v>-0.5108501827169488</v>
+        <v>-1.555188706406939</v>
       </c>
       <c r="G81">
-        <v>-5.056637086968527</v>
+        <v>-9.095753983559575</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.05333380055839</v>
       </c>
       <c r="E82">
-        <v>-12.81240627274546</v>
+        <v>-16.66198047082711</v>
       </c>
       <c r="F82">
-        <v>-0.5315312032952413</v>
+        <v>-1.369170522434282</v>
       </c>
       <c r="G82">
-        <v>-4.781464607065187</v>
+        <v>-9.277909549798437</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.461694458112881</v>
       </c>
       <c r="E83">
-        <v>-13.71320873662149</v>
+        <v>-17.84097333566281</v>
       </c>
       <c r="F83">
-        <v>-0.4519168122121808</v>
+        <v>-1.105539283023728</v>
       </c>
       <c r="G83">
-        <v>-4.65277317393544</v>
+        <v>-8.561304542195888</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.821259424747456</v>
       </c>
       <c r="E84">
-        <v>-14.38005250014729</v>
+        <v>-19.24132405768923</v>
       </c>
       <c r="F84">
-        <v>-0.6947775673649399</v>
+        <v>-1.195820561152638</v>
       </c>
       <c r="G84">
-        <v>-4.421435095716891</v>
+        <v>-8.203930158096755</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.147250787906662</v>
       </c>
       <c r="E85">
-        <v>-16.10961582425889</v>
+        <v>-19.54278074849058</v>
       </c>
       <c r="F85">
-        <v>-0.661819313509756</v>
+        <v>-1.16414544840439</v>
       </c>
       <c r="G85">
-        <v>-4.638340977835766</v>
+        <v>-8.355794560217225</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.4522335206344451</v>
       </c>
       <c r="E86">
-        <v>-15.80423019554425</v>
+        <v>-20.37672481645953</v>
       </c>
       <c r="F86">
-        <v>-0.6942921440668994</v>
+        <v>-0.5674376167369887</v>
       </c>
       <c r="G86">
-        <v>-4.31224592468276</v>
+        <v>-7.536416286413206</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.2445330273461152</v>
       </c>
       <c r="E87">
-        <v>-17.89481972048921</v>
+        <v>-21.70631312393351</v>
       </c>
       <c r="F87">
-        <v>-0.488183565474146</v>
+        <v>-0.9623253278559298</v>
       </c>
       <c r="G87">
-        <v>-3.772933971518125</v>
+        <v>-7.823941504349399</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9256145310737223</v>
       </c>
       <c r="E88">
-        <v>-19.07214299437234</v>
+        <v>-22.37309874250076</v>
       </c>
       <c r="F88">
-        <v>-0.5833538680143784</v>
+        <v>-1.011952818957648</v>
       </c>
       <c r="G88">
-        <v>-3.657439852296455</v>
+        <v>-7.637051352794554</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.573186825118899</v>
       </c>
       <c r="E89">
-        <v>-20.38288818206557</v>
+        <v>-23.15648576901257</v>
       </c>
       <c r="F89">
-        <v>-0.7900157960322018</v>
+        <v>-0.88222882694444</v>
       </c>
       <c r="G89">
-        <v>-4.081356894533884</v>
+        <v>-7.626643619482081</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.168632854232095</v>
       </c>
       <c r="E90">
-        <v>-22.13813911822124</v>
+        <v>-25.10844525314609</v>
       </c>
       <c r="F90">
-        <v>-0.5810650888804434</v>
+        <v>-0.711947966890168</v>
       </c>
       <c r="G90">
-        <v>-3.487093989215496</v>
+        <v>-7.427989452799681</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.699484331285478</v>
       </c>
       <c r="E91">
-        <v>-24.97452080076567</v>
+        <v>-26.86065188540065</v>
       </c>
       <c r="F91">
-        <v>-0.8332342085384604</v>
+        <v>-1.024305433668194</v>
       </c>
       <c r="G91">
-        <v>-3.514394545404767</v>
+        <v>-6.911806085967717</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.150568953045997</v>
       </c>
       <c r="E92">
-        <v>-25.22017494420663</v>
+        <v>-28.82411368829828</v>
       </c>
       <c r="F92">
-        <v>-0.728094504305536</v>
+        <v>-1.066044381993053</v>
       </c>
       <c r="G92">
-        <v>-3.319210058283955</v>
+        <v>-7.491260847965311</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.513740828334168</v>
       </c>
       <c r="E93">
-        <v>-26.54478770451346</v>
+        <v>-30.16609517836555</v>
       </c>
       <c r="F93">
-        <v>-0.4378503053452424</v>
+        <v>-0.5771096345320758</v>
       </c>
       <c r="G93">
-        <v>-3.549571718025427</v>
+        <v>-7.447322016496874</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.778860993091786</v>
       </c>
       <c r="E94">
-        <v>-29.78274754326689</v>
+        <v>-32.96615495126869</v>
       </c>
       <c r="F94">
-        <v>-0.9142808468609613</v>
+        <v>-0.7155869848906663</v>
       </c>
       <c r="G94">
-        <v>-2.770953694150166</v>
+        <v>-7.050439234500423</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.943850664963702</v>
       </c>
       <c r="E95">
-        <v>-31.85965016029089</v>
+        <v>-34.58954558107238</v>
       </c>
       <c r="F95">
-        <v>-1.06929241057943</v>
+        <v>-0.8116320434082549</v>
       </c>
       <c r="G95">
-        <v>-3.983618449276376</v>
+        <v>-7.491435767852916</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.001790567410451</v>
       </c>
       <c r="E96">
-        <v>-34.180502027507</v>
+        <v>-36.33821783048951</v>
       </c>
       <c r="F96">
-        <v>-1.237114676182193</v>
+        <v>-1.122172900471942</v>
       </c>
       <c r="G96">
-        <v>-3.985660051546626</v>
+        <v>-7.043236190173542</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.960145728243008</v>
       </c>
       <c r="E97">
-        <v>-35.46672250232712</v>
+        <v>-38.36299556878124</v>
       </c>
       <c r="F97">
-        <v>-0.9685248294984813</v>
+        <v>-0.9419483181144648</v>
       </c>
       <c r="G97">
-        <v>-3.89639086174269</v>
+        <v>-6.888800204630827</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.812838691823656</v>
       </c>
       <c r="E98">
-        <v>-38.5554055430379</v>
+        <v>-39.78060703707364</v>
       </c>
       <c r="F98">
-        <v>-1.347651194044356</v>
+        <v>-0.9142733915543361</v>
       </c>
       <c r="G98">
-        <v>-4.953765917844891</v>
+        <v>-7.422976823184743</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.585787856980285</v>
       </c>
       <c r="E99">
-        <v>-41.66832464843471</v>
+        <v>-42.28129087804917</v>
       </c>
       <c r="F99">
-        <v>-0.8376096451600474</v>
+        <v>-0.7533365158036426</v>
       </c>
       <c r="G99">
-        <v>-4.026134424942655</v>
+        <v>-7.604718586405911</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.269142205917367</v>
       </c>
       <c r="E100">
-        <v>-43.55755402871802</v>
+        <v>-45.52861413173442</v>
       </c>
       <c r="F100">
-        <v>-1.380862928324797</v>
+        <v>-0.9586274957698329</v>
       </c>
       <c r="G100">
-        <v>-4.673930648101821</v>
+        <v>-7.338592336510779</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.923551502673921</v>
       </c>
       <c r="E101">
-        <v>-45.78558473773271</v>
+        <v>-47.1444054231165</v>
       </c>
       <c r="F101">
-        <v>-1.374607097698855</v>
+        <v>-0.9701989600195391</v>
       </c>
       <c r="G101">
-        <v>-4.131091578994591</v>
+        <v>-7.085934917961199</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.508375652281587</v>
       </c>
       <c r="E102">
-        <v>-48.35797688713989</v>
+        <v>-48.72841530313816</v>
       </c>
       <c r="F102">
-        <v>-1.430542606572892</v>
+        <v>-1.017705830570091</v>
       </c>
       <c r="G102">
-        <v>-5.092973430187642</v>
+        <v>-7.754127583238438</v>
       </c>
     </row>
   </sheetData>
